--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128826581</v>
+      </c>
+      <c r="B3" t="n">
+        <v>86847</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>445</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kopparspindling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cortinarius cupreorufus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skyberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>562832</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6704841</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128826581</v>
       </c>
       <c r="B3" t="n">
-        <v>86847</v>
+        <v>86851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -1497,50 +1497,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826568</v>
+        <v>128826610</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>100839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562749</v>
+        <v>562833</v>
       </c>
       <c r="R10" t="n">
-        <v>6704804</v>
+        <v>6704921</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,45 +1594,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826610</v>
+        <v>128826568</v>
       </c>
       <c r="B11" t="n">
-        <v>100839</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562833</v>
+        <v>562749</v>
       </c>
       <c r="R11" t="n">
-        <v>6704921</v>
+        <v>6704804</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2302,54 +2302,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128826586</v>
+        <v>128826612</v>
       </c>
       <c r="B18" t="n">
-        <v>98651</v>
+        <v>5177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562589</v>
+        <v>562565</v>
       </c>
       <c r="R18" t="n">
-        <v>6705162</v>
+        <v>6705143</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2408,45 +2399,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128826612</v>
+        <v>128826586</v>
       </c>
       <c r="B19" t="n">
-        <v>5177</v>
+        <v>98651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562565</v>
+        <v>562589</v>
       </c>
       <c r="R19" t="n">
-        <v>6705143</v>
+        <v>6705162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128826581</v>
       </c>
       <c r="B3" t="n">
-        <v>86867</v>
+        <v>86870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,54 +883,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128826589</v>
+        <v>128826614</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>5177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562550</v>
+        <v>562511</v>
       </c>
       <c r="R4" t="n">
-        <v>6705141</v>
+        <v>6705134</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826593</v>
+        <v>128826589</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,7 +1010,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1033,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562538</v>
+        <v>562550</v>
       </c>
       <c r="R5" t="n">
-        <v>6705099</v>
+        <v>6705141</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,45 +1086,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128826614</v>
+        <v>128826593</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562511</v>
+        <v>562538</v>
       </c>
       <c r="R6" t="n">
-        <v>6705134</v>
+        <v>6705099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
         <v>128826587</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>128826609</v>
       </c>
       <c r="B9" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>128826610</v>
       </c>
       <c r="B10" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>128826564</v>
       </c>
       <c r="B12" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>128826578</v>
       </c>
       <c r="B13" t="n">
-        <v>92825</v>
+        <v>92830</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>128826600</v>
       </c>
       <c r="B14" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128826594</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>128826611</v>
       </c>
       <c r="B17" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128826586</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128826592</v>
       </c>
       <c r="B20" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128826598</v>
       </c>
       <c r="B21" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128826581</v>
       </c>
       <c r="B3" t="n">
-        <v>86870</v>
+        <v>86873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>128826589</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128826593</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>128826587</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>128826609</v>
       </c>
       <c r="B9" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,45 +1497,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826610</v>
+        <v>128826568</v>
       </c>
       <c r="B10" t="n">
-        <v>100844</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562833</v>
+        <v>562749</v>
       </c>
       <c r="R10" t="n">
-        <v>6704921</v>
+        <v>6704804</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,50 +1599,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826568</v>
+        <v>128826610</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>100847</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562749</v>
+        <v>562833</v>
       </c>
       <c r="R11" t="n">
-        <v>6704804</v>
+        <v>6704921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,7 +1699,7 @@
         <v>128826564</v>
       </c>
       <c r="B12" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>128826578</v>
       </c>
       <c r="B13" t="n">
-        <v>92830</v>
+        <v>92833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>128826600</v>
       </c>
       <c r="B14" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128826594</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>128826611</v>
       </c>
       <c r="B17" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128826586</v>
       </c>
       <c r="B19" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128826592</v>
       </c>
       <c r="B20" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128826598</v>
       </c>
       <c r="B21" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -883,45 +883,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128826614</v>
+        <v>128826589</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562511</v>
+        <v>562550</v>
       </c>
       <c r="R4" t="n">
-        <v>6705134</v>
+        <v>6705141</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,54 +989,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826589</v>
+        <v>128826614</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562550</v>
+        <v>562511</v>
       </c>
       <c r="R5" t="n">
-        <v>6705141</v>
+        <v>6705134</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1891,42 +1891,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826600</v>
+        <v>128826594</v>
       </c>
       <c r="B14" t="n">
-        <v>92855</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562838</v>
+        <v>562549</v>
       </c>
       <c r="R14" t="n">
-        <v>6704876</v>
+        <v>6705102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,42 +1997,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128826594</v>
+        <v>128826600</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>92855</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562549</v>
+        <v>562838</v>
       </c>
       <c r="R15" t="n">
-        <v>6705102</v>
+        <v>6704876</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -989,45 +989,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826614</v>
+        <v>128826593</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562511</v>
+        <v>562538</v>
       </c>
       <c r="R5" t="n">
-        <v>6705134</v>
+        <v>6705099</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,54 +1095,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128826593</v>
+        <v>128826614</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>5177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562538</v>
+        <v>562511</v>
       </c>
       <c r="R6" t="n">
-        <v>6705099</v>
+        <v>6705134</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1497,50 +1497,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826568</v>
+        <v>128826610</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>100847</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562749</v>
+        <v>562833</v>
       </c>
       <c r="R10" t="n">
-        <v>6704804</v>
+        <v>6704921</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,45 +1594,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826610</v>
+        <v>128826568</v>
       </c>
       <c r="B11" t="n">
-        <v>100847</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562833</v>
+        <v>562749</v>
       </c>
       <c r="R11" t="n">
-        <v>6704921</v>
+        <v>6704804</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128826581</v>
       </c>
       <c r="B3" t="n">
-        <v>86873</v>
+        <v>86877</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,54 +883,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128826589</v>
+        <v>128826614</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>5177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562550</v>
+        <v>562511</v>
       </c>
       <c r="R4" t="n">
-        <v>6705141</v>
+        <v>6705134</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826593</v>
+        <v>128826589</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,7 +1010,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1033,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562538</v>
+        <v>562550</v>
       </c>
       <c r="R5" t="n">
-        <v>6705099</v>
+        <v>6705141</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,45 +1086,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128826614</v>
+        <v>128826593</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562511</v>
+        <v>562538</v>
       </c>
       <c r="R6" t="n">
-        <v>6705134</v>
+        <v>6705099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
         <v>128826567</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>128826587</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>128826609</v>
       </c>
       <c r="B9" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,45 +1497,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826610</v>
+        <v>128826568</v>
       </c>
       <c r="B10" t="n">
-        <v>100847</v>
+        <v>57885</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562833</v>
+        <v>562749</v>
       </c>
       <c r="R10" t="n">
-        <v>6704921</v>
+        <v>6704804</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,50 +1599,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826568</v>
+        <v>128826610</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>100857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562749</v>
+        <v>562833</v>
       </c>
       <c r="R11" t="n">
-        <v>6704804</v>
+        <v>6704921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,7 +1699,7 @@
         <v>128826564</v>
       </c>
       <c r="B12" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>128826578</v>
       </c>
       <c r="B13" t="n">
-        <v>92833</v>
+        <v>92840</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>128826594</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128826600</v>
       </c>
       <c r="B15" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>128826573</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>128826611</v>
       </c>
       <c r="B17" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128826586</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128826592</v>
       </c>
       <c r="B20" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128826598</v>
       </c>
       <c r="B21" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>128826574</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -883,45 +883,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128826614</v>
+        <v>128826589</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562511</v>
+        <v>562550</v>
       </c>
       <c r="R4" t="n">
-        <v>6705134</v>
+        <v>6705141</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +989,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826589</v>
+        <v>128826593</v>
       </c>
       <c r="B5" t="n">
         <v>98669</v>
@@ -1010,7 +1019,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1024,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562550</v>
+        <v>562538</v>
       </c>
       <c r="R5" t="n">
-        <v>6705141</v>
+        <v>6705099</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,54 +1095,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128826593</v>
+        <v>128826614</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>5177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562538</v>
+        <v>562511</v>
       </c>
       <c r="R6" t="n">
-        <v>6705099</v>
+        <v>6705134</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128826581</v>
       </c>
       <c r="B3" t="n">
-        <v>86877</v>
+        <v>86884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,54 +883,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128826589</v>
+        <v>128826614</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>5177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562550</v>
+        <v>562511</v>
       </c>
       <c r="R4" t="n">
-        <v>6705141</v>
+        <v>6705134</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826593</v>
+        <v>128826589</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,7 +1010,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1033,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562538</v>
+        <v>562550</v>
       </c>
       <c r="R5" t="n">
-        <v>6705099</v>
+        <v>6705141</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,45 +1086,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128826614</v>
+        <v>128826593</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562511</v>
+        <v>562538</v>
       </c>
       <c r="R6" t="n">
-        <v>6705134</v>
+        <v>6705099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
         <v>128826587</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>128826609</v>
       </c>
       <c r="B9" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>128826610</v>
       </c>
       <c r="B11" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>128826564</v>
       </c>
       <c r="B12" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>128826578</v>
       </c>
       <c r="B13" t="n">
-        <v>92840</v>
+        <v>92847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,42 +1891,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826594</v>
+        <v>128826600</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562549</v>
+        <v>562838</v>
       </c>
       <c r="R14" t="n">
-        <v>6705102</v>
+        <v>6704876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,42 +1997,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128826600</v>
+        <v>128826594</v>
       </c>
       <c r="B15" t="n">
-        <v>92862</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562838</v>
+        <v>562549</v>
       </c>
       <c r="R15" t="n">
-        <v>6704876</v>
+        <v>6705102</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2208,7 +2208,7 @@
         <v>128826611</v>
       </c>
       <c r="B17" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128826586</v>
       </c>
       <c r="B19" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128826592</v>
       </c>
       <c r="B20" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128826598</v>
       </c>
       <c r="B21" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128826581</v>
       </c>
       <c r="B3" t="n">
-        <v>86884</v>
+        <v>86886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,45 +883,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128826614</v>
+        <v>128826589</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562511</v>
+        <v>562550</v>
       </c>
       <c r="R4" t="n">
-        <v>6705134</v>
+        <v>6705141</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826589</v>
+        <v>128826593</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,7 +1019,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1024,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562550</v>
+        <v>562538</v>
       </c>
       <c r="R5" t="n">
-        <v>6705141</v>
+        <v>6705099</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,54 +1095,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128826593</v>
+        <v>128826614</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>5177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562538</v>
+        <v>562511</v>
       </c>
       <c r="R6" t="n">
-        <v>6705099</v>
+        <v>6705134</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
         <v>128826567</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>128826587</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>128826609</v>
       </c>
       <c r="B9" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>128826568</v>
       </c>
       <c r="B10" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>128826610</v>
       </c>
       <c r="B11" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,34 +1696,30 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128826564</v>
+        <v>128826578</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>92849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6047725</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1731,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562531</v>
+        <v>562841</v>
       </c>
       <c r="R12" t="n">
-        <v>6705150</v>
+        <v>6704806</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1767,11 +1763,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På kapad låga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1798,30 +1789,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826578</v>
+        <v>128826564</v>
       </c>
       <c r="B13" t="n">
-        <v>92847</v>
+        <v>91542</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6047725</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1829,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562841</v>
+        <v>562531</v>
       </c>
       <c r="R13" t="n">
-        <v>6704806</v>
+        <v>6705150</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1865,6 +1860,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På kapad låga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1894,7 +1894,7 @@
         <v>128826600</v>
       </c>
       <c r="B14" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128826594</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>128826573</v>
       </c>
       <c r="B16" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>128826611</v>
       </c>
       <c r="B17" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,45 +2302,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128826612</v>
+        <v>128826586</v>
       </c>
       <c r="B18" t="n">
-        <v>5177</v>
+        <v>98678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562565</v>
+        <v>562589</v>
       </c>
       <c r="R18" t="n">
-        <v>6705143</v>
+        <v>6705162</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2399,54 +2408,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128826586</v>
+        <v>128826612</v>
       </c>
       <c r="B19" t="n">
-        <v>98676</v>
+        <v>5177</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562589</v>
+        <v>562565</v>
       </c>
       <c r="R19" t="n">
-        <v>6705162</v>
+        <v>6705143</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,7 +2508,7 @@
         <v>128826592</v>
       </c>
       <c r="B20" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128826598</v>
       </c>
       <c r="B21" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>128826574</v>
       </c>
       <c r="B22" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -1891,42 +1891,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826600</v>
+        <v>128826594</v>
       </c>
       <c r="B14" t="n">
-        <v>92871</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562838</v>
+        <v>562549</v>
       </c>
       <c r="R14" t="n">
-        <v>6704876</v>
+        <v>6705102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,42 +1997,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128826594</v>
+        <v>128826600</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>92871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562549</v>
+        <v>562838</v>
       </c>
       <c r="R15" t="n">
-        <v>6705102</v>
+        <v>6704876</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2302,54 +2302,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128826586</v>
+        <v>128826612</v>
       </c>
       <c r="B18" t="n">
-        <v>98678</v>
+        <v>5177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562589</v>
+        <v>562565</v>
       </c>
       <c r="R18" t="n">
-        <v>6705162</v>
+        <v>6705143</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2408,45 +2399,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128826612</v>
+        <v>128826586</v>
       </c>
       <c r="B19" t="n">
-        <v>5177</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562565</v>
+        <v>562589</v>
       </c>
       <c r="R19" t="n">
-        <v>6705143</v>
+        <v>6705162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -1497,50 +1497,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826568</v>
+        <v>128826610</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>100866</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562749</v>
+        <v>562833</v>
       </c>
       <c r="R10" t="n">
-        <v>6704804</v>
+        <v>6704921</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,45 +1594,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826610</v>
+        <v>128826568</v>
       </c>
       <c r="B11" t="n">
-        <v>100866</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562833</v>
+        <v>562749</v>
       </c>
       <c r="R11" t="n">
-        <v>6704921</v>
+        <v>6704804</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,30 +1696,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128826578</v>
+        <v>128826564</v>
       </c>
       <c r="B12" t="n">
-        <v>92849</v>
+        <v>91542</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6047725</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1727,10 +1731,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562841</v>
+        <v>562531</v>
       </c>
       <c r="R12" t="n">
-        <v>6704806</v>
+        <v>6705150</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,6 +1767,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På kapad låga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1789,34 +1798,30 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826564</v>
+        <v>128826578</v>
       </c>
       <c r="B13" t="n">
-        <v>91542</v>
+        <v>92849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6047725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1824,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562531</v>
+        <v>562841</v>
       </c>
       <c r="R13" t="n">
-        <v>6705150</v>
+        <v>6704806</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1860,11 +1865,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På kapad låga</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128826581</v>
       </c>
       <c r="B3" t="n">
-        <v>86886</v>
+        <v>86887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,54 +883,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128826589</v>
+        <v>128826614</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>5177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562550</v>
+        <v>562511</v>
       </c>
       <c r="R4" t="n">
-        <v>6705141</v>
+        <v>6705134</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826593</v>
+        <v>128826589</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,7 +1010,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1033,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562538</v>
+        <v>562550</v>
       </c>
       <c r="R5" t="n">
-        <v>6705099</v>
+        <v>6705141</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,45 +1086,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128826614</v>
+        <v>128826593</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562511</v>
+        <v>562538</v>
       </c>
       <c r="R6" t="n">
-        <v>6705134</v>
+        <v>6705099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
         <v>128826587</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>128826609</v>
       </c>
       <c r="B9" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,45 +1497,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826610</v>
+        <v>128826568</v>
       </c>
       <c r="B10" t="n">
-        <v>100866</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562833</v>
+        <v>562749</v>
       </c>
       <c r="R10" t="n">
-        <v>6704921</v>
+        <v>6704804</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,50 +1599,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826568</v>
+        <v>128826610</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>100892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562749</v>
+        <v>562833</v>
       </c>
       <c r="R11" t="n">
-        <v>6704804</v>
+        <v>6704921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,34 +1696,30 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128826564</v>
+        <v>128826578</v>
       </c>
       <c r="B12" t="n">
-        <v>91542</v>
+        <v>92835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6047725</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1731,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562531</v>
+        <v>562841</v>
       </c>
       <c r="R12" t="n">
-        <v>6705150</v>
+        <v>6704806</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1767,11 +1763,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På kapad låga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1798,30 +1789,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826578</v>
+        <v>128826564</v>
       </c>
       <c r="B13" t="n">
-        <v>92849</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6047725</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1829,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562841</v>
+        <v>562531</v>
       </c>
       <c r="R13" t="n">
-        <v>6704806</v>
+        <v>6705150</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1865,6 +1860,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På kapad låga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,42 +1891,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826594</v>
+        <v>128826600</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>92857</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562549</v>
+        <v>562838</v>
       </c>
       <c r="R14" t="n">
-        <v>6705102</v>
+        <v>6704876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,42 +1997,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128826600</v>
+        <v>128826594</v>
       </c>
       <c r="B15" t="n">
-        <v>92871</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562838</v>
+        <v>562549</v>
       </c>
       <c r="R15" t="n">
-        <v>6704876</v>
+        <v>6705102</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2208,7 +2208,7 @@
         <v>128826611</v>
       </c>
       <c r="B17" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128826586</v>
       </c>
       <c r="B19" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128826592</v>
       </c>
       <c r="B20" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128826598</v>
       </c>
       <c r="B21" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -983,7 +983,7 @@
         <v>128826589</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128826593</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>128826587</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>128826609</v>
       </c>
       <c r="B9" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>128826610</v>
       </c>
       <c r="B11" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>128826578</v>
       </c>
       <c r="B12" t="n">
-        <v>92835</v>
+        <v>92836</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>128826600</v>
       </c>
       <c r="B14" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128826594</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>128826611</v>
       </c>
       <c r="B17" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,45 +2302,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128826612</v>
+        <v>128826586</v>
       </c>
       <c r="B18" t="n">
-        <v>5177</v>
+        <v>98705</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562565</v>
+        <v>562589</v>
       </c>
       <c r="R18" t="n">
-        <v>6705143</v>
+        <v>6705162</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2399,54 +2408,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128826586</v>
+        <v>128826612</v>
       </c>
       <c r="B19" t="n">
-        <v>98704</v>
+        <v>5177</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562589</v>
+        <v>562565</v>
       </c>
       <c r="R19" t="n">
-        <v>6705162</v>
+        <v>6705143</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,7 +2508,7 @@
         <v>128826592</v>
       </c>
       <c r="B20" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128826598</v>
       </c>
       <c r="B21" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -983,7 +983,7 @@
         <v>128826589</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128826593</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>128826587</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>128826609</v>
       </c>
       <c r="B9" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>128826610</v>
       </c>
       <c r="B11" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,30 +1696,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128826578</v>
+        <v>128826564</v>
       </c>
       <c r="B12" t="n">
-        <v>92836</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6047725</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1727,10 +1731,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562841</v>
+        <v>562531</v>
       </c>
       <c r="R12" t="n">
-        <v>6704806</v>
+        <v>6705150</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,6 +1767,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På kapad låga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1789,34 +1798,30 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826564</v>
+        <v>128826578</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>92836</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6047725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1824,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562531</v>
+        <v>562841</v>
       </c>
       <c r="R13" t="n">
-        <v>6705150</v>
+        <v>6704806</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1860,11 +1865,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På kapad låga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,7 +2000,7 @@
         <v>128826594</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>128826611</v>
       </c>
       <c r="B17" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>128826586</v>
       </c>
       <c r="B18" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128826592</v>
       </c>
       <c r="B20" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128826581</v>
       </c>
       <c r="B3" t="n">
-        <v>86887</v>
+        <v>86890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,45 +883,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128826614</v>
+        <v>128826589</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562511</v>
+        <v>562550</v>
       </c>
       <c r="R4" t="n">
-        <v>6705134</v>
+        <v>6705141</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826589</v>
+        <v>128826593</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,7 +1019,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1024,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562550</v>
+        <v>562538</v>
       </c>
       <c r="R5" t="n">
-        <v>6705141</v>
+        <v>6705099</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,54 +1095,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128826593</v>
+        <v>128826614</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>5177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562538</v>
+        <v>562511</v>
       </c>
       <c r="R6" t="n">
-        <v>6705099</v>
+        <v>6705134</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
         <v>128826587</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>128826609</v>
       </c>
       <c r="B9" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>128826610</v>
       </c>
       <c r="B11" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>128826564</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>128826578</v>
       </c>
       <c r="B13" t="n">
-        <v>92836</v>
+        <v>92839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>128826600</v>
       </c>
       <c r="B14" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128826594</v>
       </c>
       <c r="B15" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>128826611</v>
       </c>
       <c r="B17" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,54 +2302,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128826586</v>
+        <v>128826612</v>
       </c>
       <c r="B18" t="n">
-        <v>98706</v>
+        <v>5177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562589</v>
+        <v>562565</v>
       </c>
       <c r="R18" t="n">
-        <v>6705162</v>
+        <v>6705143</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2408,45 +2399,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128826612</v>
+        <v>128826586</v>
       </c>
       <c r="B19" t="n">
-        <v>5177</v>
+        <v>98710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562565</v>
+        <v>562589</v>
       </c>
       <c r="R19" t="n">
-        <v>6705143</v>
+        <v>6705162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,7 +2508,7 @@
         <v>128826592</v>
       </c>
       <c r="B20" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128826598</v>
       </c>
       <c r="B21" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -2302,45 +2302,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128826612</v>
+        <v>128826586</v>
       </c>
       <c r="B18" t="n">
-        <v>5177</v>
+        <v>98710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562565</v>
+        <v>562589</v>
       </c>
       <c r="R18" t="n">
-        <v>6705143</v>
+        <v>6705162</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2399,54 +2408,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128826586</v>
+        <v>128826612</v>
       </c>
       <c r="B19" t="n">
-        <v>98710</v>
+        <v>5177</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562589</v>
+        <v>562565</v>
       </c>
       <c r="R19" t="n">
-        <v>6705162</v>
+        <v>6705143</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -886,7 +886,7 @@
         <v>128826589</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>128826593</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>128826587</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>128826609</v>
       </c>
       <c r="B9" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,50 +1497,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826568</v>
+        <v>128826610</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>100901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562749</v>
+        <v>562833</v>
       </c>
       <c r="R10" t="n">
-        <v>6704804</v>
+        <v>6704921</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,45 +1594,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826610</v>
+        <v>128826568</v>
       </c>
       <c r="B11" t="n">
-        <v>100899</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562833</v>
+        <v>562749</v>
       </c>
       <c r="R11" t="n">
-        <v>6704921</v>
+        <v>6704804</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,7 +1699,7 @@
         <v>128826564</v>
       </c>
       <c r="B12" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>128826578</v>
       </c>
       <c r="B13" t="n">
-        <v>92839</v>
+        <v>92841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>128826600</v>
       </c>
       <c r="B14" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128826594</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>128826611</v>
       </c>
       <c r="B17" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,54 +2302,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128826586</v>
+        <v>128826612</v>
       </c>
       <c r="B18" t="n">
-        <v>98710</v>
+        <v>5177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562589</v>
+        <v>562565</v>
       </c>
       <c r="R18" t="n">
-        <v>6705162</v>
+        <v>6705143</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2408,45 +2399,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128826612</v>
+        <v>128826586</v>
       </c>
       <c r="B19" t="n">
-        <v>5177</v>
+        <v>98712</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562565</v>
+        <v>562589</v>
       </c>
       <c r="R19" t="n">
-        <v>6705143</v>
+        <v>6705162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,7 +2508,7 @@
         <v>128826592</v>
       </c>
       <c r="B20" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128826598</v>
       </c>
       <c r="B21" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -883,54 +883,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128826589</v>
+        <v>128826614</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>5177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562550</v>
+        <v>562511</v>
       </c>
       <c r="R4" t="n">
-        <v>6705141</v>
+        <v>6705134</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826593</v>
+        <v>128826589</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,7 +1010,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1033,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562538</v>
+        <v>562550</v>
       </c>
       <c r="R5" t="n">
-        <v>6705099</v>
+        <v>6705141</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,45 +1086,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128826614</v>
+        <v>128826593</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562511</v>
+        <v>562538</v>
       </c>
       <c r="R6" t="n">
-        <v>6705134</v>
+        <v>6705099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
         <v>128826587</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>128826609</v>
       </c>
       <c r="B9" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,45 +1497,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826610</v>
+        <v>128826568</v>
       </c>
       <c r="B10" t="n">
-        <v>100901</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562833</v>
+        <v>562749</v>
       </c>
       <c r="R10" t="n">
-        <v>6704921</v>
+        <v>6704804</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,50 +1599,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826568</v>
+        <v>128826610</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>100905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562749</v>
+        <v>562833</v>
       </c>
       <c r="R11" t="n">
-        <v>6704804</v>
+        <v>6704921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,7 +1699,7 @@
         <v>128826564</v>
       </c>
       <c r="B12" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>128826578</v>
       </c>
       <c r="B13" t="n">
-        <v>92841</v>
+        <v>92845</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,42 +1891,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826600</v>
+        <v>128826594</v>
       </c>
       <c r="B14" t="n">
-        <v>92863</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562838</v>
+        <v>562549</v>
       </c>
       <c r="R14" t="n">
-        <v>6704876</v>
+        <v>6705102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,42 +1997,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128826594</v>
+        <v>128826600</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>92867</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562549</v>
+        <v>562838</v>
       </c>
       <c r="R15" t="n">
-        <v>6705102</v>
+        <v>6704876</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2208,7 +2208,7 @@
         <v>128826611</v>
       </c>
       <c r="B17" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128826586</v>
       </c>
       <c r="B19" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128826592</v>
       </c>
       <c r="B20" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128826598</v>
       </c>
       <c r="B21" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -983,7 +983,7 @@
         <v>128826589</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128826593</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>128826587</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>128826609</v>
       </c>
       <c r="B9" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>128826610</v>
       </c>
       <c r="B11" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>128826564</v>
       </c>
       <c r="B12" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>128826578</v>
       </c>
       <c r="B13" t="n">
-        <v>92845</v>
+        <v>92846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,42 +1891,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826594</v>
+        <v>128826600</v>
       </c>
       <c r="B14" t="n">
-        <v>98716</v>
+        <v>92868</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562549</v>
+        <v>562838</v>
       </c>
       <c r="R14" t="n">
-        <v>6705102</v>
+        <v>6704876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,42 +1997,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128826600</v>
+        <v>128826594</v>
       </c>
       <c r="B15" t="n">
-        <v>92867</v>
+        <v>98724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562838</v>
+        <v>562549</v>
       </c>
       <c r="R15" t="n">
-        <v>6704876</v>
+        <v>6705102</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2208,7 +2208,7 @@
         <v>128826611</v>
       </c>
       <c r="B17" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128826586</v>
       </c>
       <c r="B19" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128826592</v>
       </c>
       <c r="B20" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128826598</v>
       </c>
       <c r="B21" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -883,45 +883,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128826614</v>
+        <v>128826589</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562511</v>
+        <v>562550</v>
       </c>
       <c r="R4" t="n">
-        <v>6705134</v>
+        <v>6705141</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +989,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826589</v>
+        <v>128826593</v>
       </c>
       <c r="B5" t="n">
         <v>98724</v>
@@ -1010,7 +1019,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1024,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562550</v>
+        <v>562538</v>
       </c>
       <c r="R5" t="n">
-        <v>6705141</v>
+        <v>6705099</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,54 +1095,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128826593</v>
+        <v>128826614</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>5177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562538</v>
+        <v>562511</v>
       </c>
       <c r="R6" t="n">
-        <v>6705099</v>
+        <v>6705134</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119477693</v>
+        <v>128826581</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562577</v>
+        <v>562832</v>
       </c>
       <c r="R2" t="n">
-        <v>6705156</v>
+        <v>6704841</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128826581</v>
+        <v>127843705</v>
       </c>
       <c r="B3" t="n">
-        <v>86890</v>
+        <v>92557</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>445</v>
+        <v>483</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562832</v>
+        <v>562721</v>
       </c>
       <c r="R3" t="n">
-        <v>6704841</v>
+        <v>6705209</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,54 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128826589</v>
+        <v>128826564</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562550</v>
+        <v>562531</v>
       </c>
       <c r="R4" t="n">
-        <v>6705141</v>
+        <v>6705150</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På kapad låga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,42 +971,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826593</v>
+        <v>128826598</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>93233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1033,10 +1015,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562538</v>
+        <v>562818</v>
       </c>
       <c r="R5" t="n">
-        <v>6705099</v>
+        <v>6704908</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,45 +1077,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128826614</v>
+        <v>128826600</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>93233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562511</v>
+        <v>562838</v>
       </c>
       <c r="R6" t="n">
-        <v>6705134</v>
+        <v>6704876</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,38 +1183,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128826567</v>
+        <v>128826573</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1232,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562819</v>
+        <v>562579</v>
       </c>
       <c r="R7" t="n">
-        <v>6704912</v>
+        <v>6705151</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,42 +1285,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128826587</v>
+        <v>128826574</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1338,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562559</v>
+        <v>562568</v>
       </c>
       <c r="R8" t="n">
-        <v>6705137</v>
+        <v>6705159</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128826609</v>
+        <v>128826612</v>
       </c>
       <c r="B9" t="n">
-        <v>100913</v>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1411,21 +1398,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1435,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562838</v>
+        <v>562565</v>
       </c>
       <c r="R9" t="n">
-        <v>6704885</v>
+        <v>6705143</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,50 +1484,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826568</v>
+        <v>128826614</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562749</v>
+        <v>562511</v>
       </c>
       <c r="R10" t="n">
-        <v>6704804</v>
+        <v>6705134</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,10 +1581,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826610</v>
+        <v>128826615</v>
       </c>
       <c r="B11" t="n">
-        <v>100913</v>
+        <v>5179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1610,21 +1592,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1616,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562833</v>
+        <v>562508</v>
       </c>
       <c r="R11" t="n">
-        <v>6704921</v>
+        <v>6705143</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,10 +1678,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128826564</v>
+        <v>128826567</v>
       </c>
       <c r="B12" t="n">
-        <v>91550</v>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1707,34 +1689,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562531</v>
+        <v>562819</v>
       </c>
       <c r="R12" t="n">
-        <v>6705150</v>
+        <v>6704912</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1767,11 +1754,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På kapad låga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1798,41 +1780,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826578</v>
+        <v>128826568</v>
       </c>
       <c r="B13" t="n">
-        <v>92846</v>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6047725</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562841</v>
+        <v>562749</v>
       </c>
       <c r="R13" t="n">
-        <v>6704806</v>
+        <v>6704804</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,54 +1882,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826600</v>
+        <v>106908357</v>
       </c>
       <c r="B14" t="n">
-        <v>92868</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skyberget, Dlr</t>
+          <t>Storåsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562838</v>
+        <v>562548</v>
       </c>
       <c r="R14" t="n">
-        <v>6704876</v>
+        <v>6705193</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1965,12 +1947,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1985,22 +1967,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128826594</v>
+        <v>119477693</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,7 +2009,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2041,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562549</v>
+        <v>562577</v>
       </c>
       <c r="R15" t="n">
-        <v>6705102</v>
+        <v>6705156</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,12 +2053,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,38 +2085,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128826573</v>
+        <v>119477695</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2143,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562579</v>
+        <v>562604</v>
       </c>
       <c r="R16" t="n">
-        <v>6705151</v>
+        <v>6705178</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,12 +2159,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,45 +2191,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128826611</v>
+        <v>128826583</v>
       </c>
       <c r="B17" t="n">
-        <v>100913</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562831</v>
+        <v>562631</v>
       </c>
       <c r="R17" t="n">
-        <v>6704838</v>
+        <v>6705159</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,45 +2297,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128826612</v>
+        <v>128826585</v>
       </c>
       <c r="B18" t="n">
-        <v>5177</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562565</v>
+        <v>562608</v>
       </c>
       <c r="R18" t="n">
-        <v>6705143</v>
+        <v>6705172</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2402,7 +2406,7 @@
         <v>128826586</v>
       </c>
       <c r="B19" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,10 +2509,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128826592</v>
+        <v>128826587</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,7 +2539,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2543,21 +2547,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skyberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562548</v>
+        <v>562559</v>
       </c>
       <c r="R20" t="n">
-        <v>6705133</v>
+        <v>6705137</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2616,42 +2615,47 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128826598</v>
+        <v>128826588</v>
       </c>
       <c r="B21" t="n">
-        <v>92868</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2660,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562818</v>
+        <v>562566</v>
       </c>
       <c r="R21" t="n">
-        <v>6704908</v>
+        <v>6705195</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2722,38 +2726,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128826574</v>
+        <v>128826589</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2762,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562568</v>
+        <v>562550</v>
       </c>
       <c r="R22" t="n">
-        <v>6705159</v>
+        <v>6705141</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,6 +2829,1644 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128826590</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skyberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>562604</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6705171</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128826591</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skyberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>562601</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6705173</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128826592</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skyberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>562548</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6705133</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128826593</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skyberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>562538</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6705099</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128826594</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skyberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>562549</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6705102</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128826595</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skyberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>562598</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6705149</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128826596</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skyberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>562611</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6705168</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>106908353</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Storåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>562478</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6705020</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>80223237</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Österby, Daniels hage, Hedemora kommun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>562703</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6705191</v>
+      </c>
+      <c r="S31" t="n">
+        <v>14</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2019-10-02</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2019-10-02</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127843712</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skyberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>562722</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6705205</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128826606</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skyberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>562897</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6704845</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128826608</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skyberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>562887</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6704837</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128826609</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skyberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>562838</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6704885</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128826610</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skyberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>562833</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6704921</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128826611</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skyberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>562831</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6704838</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128826578</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93211</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skyberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>562841</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6704806</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45277-2025 artfynd.xlsx
+++ b/artfynd/A 45277-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826581</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843705</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826564</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826598</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826600</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826573</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826574</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826612</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1578,6 +1623,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826614</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1675,6 +1725,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826615</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1777,6 +1832,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826567</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1879,6 +1939,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826568</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1976,6 +2041,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106908357</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2082,6 +2152,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119477693</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2188,6 +2263,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119477695</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2294,6 +2374,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826583</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2400,6 +2485,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826585</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2506,6 +2596,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826586</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2612,6 +2707,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826587</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2723,6 +2823,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826588</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2829,6 +2934,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826589</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2940,6 +3050,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826590</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3051,6 +3166,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826591</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3162,6 +3282,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826592</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3268,6 +3393,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826593</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3374,6 +3504,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826594</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3480,6 +3615,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826595</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3586,6 +3726,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826596</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3683,6 +3828,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106908353</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3792,6 +3942,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80223237</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3889,6 +4044,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843712</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3986,6 +4146,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826606</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4083,6 +4248,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826608</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4180,6 +4350,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826609</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4277,6 +4452,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826610</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4374,6 +4554,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826611</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4467,8 +4652,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826578</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>